--- a/products/Catering_Business_Manager_PREMIUM_Classic.xlsx
+++ b/products/Catering_Business_Manager_PREMIUM_Classic.xlsx
@@ -5778,58 +5778,57 @@
             </a:ln>
           </c:spPr>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:f>'_Data'!$Q$26:$Q$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -6854,11 +6853,11 @@
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=1)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=1)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=1)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=1)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K2" s="1">
@@ -6901,11 +6900,11 @@
         <v>2</v>
       </c>
       <c r="I3" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=2)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=2)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=2)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=2)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K3" s="1">
@@ -6948,11 +6947,11 @@
         <v>3</v>
       </c>
       <c r="I4" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=3)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=3)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=3)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=3)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K4" s="1">
@@ -6995,11 +6994,11 @@
         <v>4</v>
       </c>
       <c r="I5" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=4)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=4)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=4)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=4)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K5" s="1">
@@ -7042,11 +7041,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=5)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=5)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=5)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=5)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K6" s="1">
@@ -7089,11 +7088,11 @@
         <v>6</v>
       </c>
       <c r="I7" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=6)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=6)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=6)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=6)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K7" s="1">
@@ -7136,11 +7135,11 @@
         <v>7</v>
       </c>
       <c r="I8" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=7)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=7)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=7)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=7)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K8" s="1">
@@ -7183,11 +7182,11 @@
         <v>8</v>
       </c>
       <c r="I9" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=8)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=8)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=8)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=8)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K9" s="1">
@@ -7230,11 +7229,11 @@
         <v>9</v>
       </c>
       <c r="I10" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=9)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=9)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=9)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=9)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K10" s="1">
@@ -7277,11 +7276,11 @@
         <v>10</v>
       </c>
       <c r="I11" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=10)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=10)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=10)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=10)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K11" s="1">
@@ -7324,11 +7323,11 @@
         <v>11</v>
       </c>
       <c r="I12" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=11)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=11)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=11)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=11)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K12" s="1">
@@ -7371,11 +7370,11 @@
         <v>12</v>
       </c>
       <c r="I13" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=12)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=12)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=12)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=12)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K13" s="1">
@@ -7702,7 +7701,7 @@
         <v>82</v>
       </c>
       <c r="AF24" s="1">
-        <f>SUMPRODUCT(('🛒 Shopping List'!$G$8:$G$47&gt;0)*('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓"))</f>
+        <f>SUMPRODUCT(ISNUMBER('🛒 Shopping List'!$G$8:$G$47)*('🛒 Shopping List'!$G$8:$G$47&gt;0)*('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓"))</f>
         <v>0</v>
       </c>
     </row>
@@ -7735,26 +7734,26 @@
         <v>83</v>
       </c>
       <c r="AF25" s="1">
-        <f>SUMPRODUCT(('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓")*('🛒 Shopping List'!$G$8:$G$47&gt;0)*'🛒 Shopping List'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(ISNUMBER('🛒 Shopping List'!$G$8:$G$47)*('🛒 Shopping List'!$G$8:$G$47&gt;0)*('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓"),'🛒 Shopping List'!$I$8:$I$47)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="14:32">
       <c r="Q26" s="1">
         <f>IF('👥 Clients'!$C$8="","",'👥 Clients'!$C$8)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R26" s="1">
         <f>IF($Q26="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q26,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T26" s="1">
         <f>IF('🍽️ Menu Costing'!$C$8="","",'🍽️ Menu Costing'!$C$8)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U26" s="1">
         <f>IF($T26="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T26,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA26" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),25),"")</f>
@@ -7785,19 +7784,19 @@
       </c>
       <c r="Q27" s="1">
         <f>IF('👥 Clients'!$C$9="","",'👥 Clients'!$C$9)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R27" s="1">
         <f>IF($Q27="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q27,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T27" s="1">
         <f>IF('🍽️ Menu Costing'!$C$9="","",'🍽️ Menu Costing'!$C$9)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U27" s="1">
         <f>IF($T27="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T27,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA27" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),26),"")</f>
@@ -7829,19 +7828,19 @@
       </c>
       <c r="Q28" s="1">
         <f>IF('👥 Clients'!$C$10="","",'👥 Clients'!$C$10)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R28" s="1">
         <f>IF($Q28="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q28,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T28" s="1">
         <f>IF('🍽️ Menu Costing'!$C$10="","",'🍽️ Menu Costing'!$C$10)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U28" s="1">
         <f>IF($T28="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T28,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA28" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),27),"")</f>
@@ -7873,19 +7872,19 @@
       </c>
       <c r="Q29" s="1">
         <f>IF('👥 Clients'!$C$11="","",'👥 Clients'!$C$11)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R29" s="1">
         <f>IF($Q29="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q29,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T29" s="1">
         <f>IF('🍽️ Menu Costing'!$C$11="","",'🍽️ Menu Costing'!$C$11)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U29" s="1">
         <f>IF($T29="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T29,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA29" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),28),"")</f>
@@ -7917,19 +7916,19 @@
       </c>
       <c r="Q30" s="1">
         <f>IF('👥 Clients'!$C$12="","",'👥 Clients'!$C$12)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R30" s="1">
         <f>IF($Q30="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q30,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T30" s="1">
         <f>IF('🍽️ Menu Costing'!$C$12="","",'🍽️ Menu Costing'!$C$12)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U30" s="1">
         <f>IF($T30="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T30,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA30" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),29),"")</f>
@@ -7961,19 +7960,19 @@
       </c>
       <c r="Q31" s="1">
         <f>IF('👥 Clients'!$C$13="","",'👥 Clients'!$C$13)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R31" s="1">
         <f>IF($Q31="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q31,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T31" s="1">
         <f>IF('🍽️ Menu Costing'!$C$13="","",'🍽️ Menu Costing'!$C$13)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U31" s="1">
         <f>IF($T31="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T31,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA31" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),30),"")</f>
@@ -8005,19 +8004,19 @@
       </c>
       <c r="Q32" s="1">
         <f>IF('👥 Clients'!$C$14="","",'👥 Clients'!$C$14)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R32" s="1">
         <f>IF($Q32="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q32,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T32" s="1">
         <f>IF('🍽️ Menu Costing'!$C$14="","",'🍽️ Menu Costing'!$C$14)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U32" s="1">
         <f>IF($T32="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T32,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA32" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),31),"")</f>
@@ -8049,19 +8048,19 @@
       </c>
       <c r="Q33" s="1">
         <f>IF('👥 Clients'!$C$15="","",'👥 Clients'!$C$15)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R33" s="1">
         <f>IF($Q33="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q33,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T33" s="1">
         <f>IF('🍽️ Menu Costing'!$C$15="","",'🍽️ Menu Costing'!$C$15)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U33" s="1">
         <f>IF($T33="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T33,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA33" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),32),"")</f>
@@ -8086,19 +8085,19 @@
     <row r="34" spans="14:32">
       <c r="Q34" s="1">
         <f>IF('👥 Clients'!$C$16="","",'👥 Clients'!$C$16)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R34" s="1">
         <f>IF($Q34="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q34,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T34" s="1">
         <f>IF('🍽️ Menu Costing'!$C$16="","",'🍽️ Menu Costing'!$C$16)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U34" s="1">
         <f>IF($T34="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T34,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA34" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),33),"")</f>
@@ -8123,19 +8122,19 @@
     <row r="35" spans="14:32">
       <c r="Q35" s="1">
         <f>IF('👥 Clients'!$C$17="","",'👥 Clients'!$C$17)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R35" s="1">
         <f>IF($Q35="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q35,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T35" s="1">
         <f>IF('🍽️ Menu Costing'!$C$17="","",'🍽️ Menu Costing'!$C$17)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U35" s="1">
         <f>IF($T35="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T35,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA35" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),34),"")</f>
@@ -8160,19 +8159,19 @@
     <row r="36" spans="14:32">
       <c r="Q36" s="1">
         <f>IF('👥 Clients'!$C$18="","",'👥 Clients'!$C$18)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R36" s="1">
         <f>IF($Q36="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q36,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T36" s="1">
         <f>IF('🍽️ Menu Costing'!$C$18="","",'🍽️ Menu Costing'!$C$18)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U36" s="1">
         <f>IF($T36="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T36,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA36" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),35),"")</f>
@@ -8197,19 +8196,19 @@
     <row r="37" spans="14:32">
       <c r="Q37" s="1">
         <f>IF('👥 Clients'!$C$19="","",'👥 Clients'!$C$19)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R37" s="1">
         <f>IF($Q37="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q37,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T37" s="1">
         <f>IF('🍽️ Menu Costing'!$C$19="","",'🍽️ Menu Costing'!$C$19)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U37" s="1">
         <f>IF($T37="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T37,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA37" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),36),"")</f>
@@ -8227,19 +8226,19 @@
     <row r="38" spans="14:32">
       <c r="Q38" s="1">
         <f>IF('👥 Clients'!$C$20="","",'👥 Clients'!$C$20)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R38" s="1">
         <f>IF($Q38="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q38,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T38" s="1">
         <f>IF('🍽️ Menu Costing'!$C$20="","",'🍽️ Menu Costing'!$C$20)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U38" s="1">
         <f>IF($T38="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T38,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA38" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),37),"")</f>
@@ -8257,19 +8256,19 @@
     <row r="39" spans="14:32">
       <c r="Q39" s="1">
         <f>IF('👥 Clients'!$C$21="","",'👥 Clients'!$C$21)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R39" s="1">
         <f>IF($Q39="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q39,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T39" s="1">
         <f>IF('🍽️ Menu Costing'!$C$21="","",'🍽️ Menu Costing'!$C$21)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U39" s="1">
         <f>IF($T39="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T39,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA39" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),38),"")</f>
@@ -8287,19 +8286,19 @@
     <row r="40" spans="14:32">
       <c r="Q40" s="1">
         <f>IF('👥 Clients'!$C$22="","",'👥 Clients'!$C$22)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R40" s="1">
         <f>IF($Q40="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q40,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T40" s="1">
         <f>IF('🍽️ Menu Costing'!$C$22="","",'🍽️ Menu Costing'!$C$22)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U40" s="1">
         <f>IF($T40="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T40,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA40" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),39),"")</f>
@@ -8327,7 +8326,7 @@
     </row>
     <row r="42" spans="14:32">
       <c r="AA42" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),1),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),1),"")</f>
         <v/>
       </c>
       <c r="AB42" s="1">
@@ -8336,12 +8335,12 @@
       </c>
       <c r="AC42" s="1">
         <f>IF($AA42="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA42,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="14:32">
       <c r="AA43" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),2),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),2),"")</f>
         <v/>
       </c>
       <c r="AB43" s="1">
@@ -8350,12 +8349,12 @@
       </c>
       <c r="AC43" s="1">
         <f>IF($AA43="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA43,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="14:32">
       <c r="AA44" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),3),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),3),"")</f>
         <v/>
       </c>
       <c r="AB44" s="1">
@@ -8364,12 +8363,12 @@
       </c>
       <c r="AC44" s="1">
         <f>IF($AA44="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA44,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="45" spans="14:32">
       <c r="AA45" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),4),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),4),"")</f>
         <v/>
       </c>
       <c r="AB45" s="1">
@@ -8378,12 +8377,12 @@
       </c>
       <c r="AC45" s="1">
         <f>IF($AA45="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA45,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="46" spans="14:32">
       <c r="AA46" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),5),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),5),"")</f>
         <v/>
       </c>
       <c r="AB46" s="1">
@@ -8392,12 +8391,12 @@
       </c>
       <c r="AC46" s="1">
         <f>IF($AA46="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA46,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="14:32">
       <c r="AA47" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),6),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),6),"")</f>
         <v/>
       </c>
       <c r="AB47" s="1">
@@ -8406,12 +8405,12 @@
       </c>
       <c r="AC47" s="1">
         <f>IF($AA47="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA47,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="14:32">
       <c r="AA48" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),7),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),7),"")</f>
         <v/>
       </c>
       <c r="AB48" s="1">
@@ -8420,12 +8419,12 @@
       </c>
       <c r="AC48" s="1">
         <f>IF($AA48="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA48,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="49" spans="27:29">
       <c r="AA49" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),8),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),8),"")</f>
         <v/>
       </c>
       <c r="AB49" s="1">
@@ -8434,12 +8433,12 @@
       </c>
       <c r="AC49" s="1">
         <f>IF($AA49="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA49,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="50" spans="27:29">
       <c r="AA50" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),9),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),9),"")</f>
         <v/>
       </c>
       <c r="AB50" s="1">
@@ -8448,12 +8447,12 @@
       </c>
       <c r="AC50" s="1">
         <f>IF($AA50="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA50,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="27:29">
       <c r="AA51" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),10),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),10),"")</f>
         <v/>
       </c>
       <c r="AB51" s="1">
@@ -8462,12 +8461,12 @@
       </c>
       <c r="AC51" s="1">
         <f>IF($AA51="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA51,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="52" spans="27:29">
       <c r="AA52" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),11),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),11),"")</f>
         <v/>
       </c>
       <c r="AB52" s="1">
@@ -8476,12 +8475,12 @@
       </c>
       <c r="AC52" s="1">
         <f>IF($AA52="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA52,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="53" spans="27:29">
       <c r="AA53" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),12),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),12),"")</f>
         <v/>
       </c>
       <c r="AB53" s="1">
@@ -8490,12 +8489,12 @@
       </c>
       <c r="AC53" s="1">
         <f>IF($AA53="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA53,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="54" spans="27:29">
       <c r="AA54" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),13),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),13),"")</f>
         <v/>
       </c>
       <c r="AB54" s="1">
@@ -8504,12 +8503,12 @@
       </c>
       <c r="AC54" s="1">
         <f>IF($AA54="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA54,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="27:29">
       <c r="AA55" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),14),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),14),"")</f>
         <v/>
       </c>
       <c r="AB55" s="1">
@@ -8518,12 +8517,12 @@
       </c>
       <c r="AC55" s="1">
         <f>IF($AA55="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA55,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="27:29">
       <c r="AA56" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),15),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),15),"")</f>
         <v/>
       </c>
       <c r="AB56" s="1">
@@ -8532,12 +8531,12 @@
       </c>
       <c r="AC56" s="1">
         <f>IF($AA56="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA56,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="57" spans="27:29">
       <c r="AA57" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),16),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),16),"")</f>
         <v/>
       </c>
       <c r="AB57" s="1">
@@ -8546,12 +8545,12 @@
       </c>
       <c r="AC57" s="1">
         <f>IF($AA57="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA57,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="58" spans="27:29">
       <c r="AA58" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),17),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),17),"")</f>
         <v/>
       </c>
       <c r="AB58" s="1">
@@ -8560,12 +8559,12 @@
       </c>
       <c r="AC58" s="1">
         <f>IF($AA58="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA58,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="59" spans="27:29">
       <c r="AA59" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),18),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),18),"")</f>
         <v/>
       </c>
       <c r="AB59" s="1">
@@ -8574,12 +8573,12 @@
       </c>
       <c r="AC59" s="1">
         <f>IF($AA59="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA59,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="60" spans="27:29">
       <c r="AA60" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),19),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),19),"")</f>
         <v/>
       </c>
       <c r="AB60" s="1">
@@ -8588,12 +8587,12 @@
       </c>
       <c r="AC60" s="1">
         <f>IF($AA60="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA60,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="61" spans="27:29">
       <c r="AA61" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),20),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),20),"")</f>
         <v/>
       </c>
       <c r="AB61" s="1">
@@ -8602,12 +8601,12 @@
       </c>
       <c r="AC61" s="1">
         <f>IF($AA61="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA61,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="62" spans="27:29">
       <c r="AA62" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),21),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),21),"")</f>
         <v/>
       </c>
       <c r="AB62" s="1">
@@ -8616,12 +8615,12 @@
       </c>
       <c r="AC62" s="1">
         <f>IF($AA62="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA62,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="63" spans="27:29">
       <c r="AA63" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),22),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),22),"")</f>
         <v/>
       </c>
       <c r="AB63" s="1">
@@ -8630,12 +8629,12 @@
       </c>
       <c r="AC63" s="1">
         <f>IF($AA63="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA63,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="64" spans="27:29">
       <c r="AA64" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),23),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),23),"")</f>
         <v/>
       </c>
       <c r="AB64" s="1">
@@ -8644,12 +8643,12 @@
       </c>
       <c r="AC64" s="1">
         <f>IF($AA64="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA64,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="65" spans="27:29">
       <c r="AA65" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),24),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),24),"")</f>
         <v/>
       </c>
       <c r="AB65" s="1">
@@ -8658,12 +8657,12 @@
       </c>
       <c r="AC65" s="1">
         <f>IF($AA65="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA65,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="66" spans="27:29">
       <c r="AA66" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),25),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),25),"")</f>
         <v/>
       </c>
       <c r="AB66" s="1">
@@ -8672,12 +8671,12 @@
       </c>
       <c r="AC66" s="1">
         <f>IF($AA66="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA66,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="27:29">
       <c r="AA67" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),26),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),26),"")</f>
         <v/>
       </c>
       <c r="AB67" s="1">
@@ -8686,12 +8685,12 @@
       </c>
       <c r="AC67" s="1">
         <f>IF($AA67="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA67,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="68" spans="27:29">
       <c r="AA68" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),27),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),27),"")</f>
         <v/>
       </c>
       <c r="AB68" s="1">
@@ -8700,12 +8699,12 @@
       </c>
       <c r="AC68" s="1">
         <f>IF($AA68="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA68,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="27:29">
       <c r="AA69" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),28),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),28),"")</f>
         <v/>
       </c>
       <c r="AB69" s="1">
@@ -8714,12 +8713,12 @@
       </c>
       <c r="AC69" s="1">
         <f>IF($AA69="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA69,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="70" spans="27:29">
       <c r="AA70" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),29),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),29),"")</f>
         <v/>
       </c>
       <c r="AB70" s="1">
@@ -8728,12 +8727,12 @@
       </c>
       <c r="AC70" s="1">
         <f>IF($AA70="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA70,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="71" spans="27:29">
       <c r="AA71" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),30),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),30),"")</f>
         <v/>
       </c>
       <c r="AB71" s="1">
@@ -8742,12 +8741,12 @@
       </c>
       <c r="AC71" s="1">
         <f>IF($AA71="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA71,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="72" spans="27:29">
       <c r="AA72" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),31),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),31),"")</f>
         <v/>
       </c>
       <c r="AB72" s="1">
@@ -8756,12 +8755,12 @@
       </c>
       <c r="AC72" s="1">
         <f>IF($AA72="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA72,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="27:29">
       <c r="AA73" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),32),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),32),"")</f>
         <v/>
       </c>
       <c r="AB73" s="1">
@@ -8770,12 +8769,12 @@
       </c>
       <c r="AC73" s="1">
         <f>IF($AA73="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA73,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="27:29">
       <c r="AA74" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),33),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),33),"")</f>
         <v/>
       </c>
       <c r="AB74" s="1">
@@ -8784,12 +8783,12 @@
       </c>
       <c r="AC74" s="1">
         <f>IF($AA74="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA74,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="75" spans="27:29">
       <c r="AA75" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),34),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),34),"")</f>
         <v/>
       </c>
       <c r="AB75" s="1">
@@ -8798,12 +8797,12 @@
       </c>
       <c r="AC75" s="1">
         <f>IF($AA75="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA75,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="76" spans="27:29">
       <c r="AA76" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),35),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),35),"")</f>
         <v/>
       </c>
       <c r="AB76" s="1">
@@ -8812,12 +8811,12 @@
       </c>
       <c r="AC76" s="1">
         <f>IF($AA76="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA76,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="77" spans="27:29">
       <c r="AA77" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),36),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),36),"")</f>
         <v/>
       </c>
       <c r="AB77" s="1">
@@ -8826,12 +8825,12 @@
       </c>
       <c r="AC77" s="1">
         <f>IF($AA77="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA77,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="78" spans="27:29">
       <c r="AA78" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),37),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),37),"")</f>
         <v/>
       </c>
       <c r="AB78" s="1">
@@ -8840,12 +8839,12 @@
       </c>
       <c r="AC78" s="1">
         <f>IF($AA78="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA78,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="79" spans="27:29">
       <c r="AA79" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),38),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),38),"")</f>
         <v/>
       </c>
       <c r="AB79" s="1">
@@ -8854,12 +8853,12 @@
       </c>
       <c r="AC79" s="1">
         <f>IF($AA79="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA79,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="80" spans="27:29">
       <c r="AA80" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),39),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),39),"")</f>
         <v/>
       </c>
       <c r="AB80" s="1">
@@ -8868,12 +8867,12 @@
       </c>
       <c r="AC80" s="1">
         <f>IF($AA80="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA80,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="81" spans="27:29">
       <c r="AA81" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),40),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),40),"")</f>
         <v/>
       </c>
       <c r="AB81" s="1">
@@ -8882,12 +8881,12 @@
       </c>
       <c r="AC81" s="1">
         <f>IF($AA81="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA81,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="82" spans="27:29">
       <c r="AA82" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),41),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),41),"")</f>
         <v/>
       </c>
       <c r="AB82" s="1">
@@ -8896,12 +8895,12 @@
       </c>
       <c r="AC82" s="1">
         <f>IF($AA82="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA82,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="83" spans="27:29">
       <c r="AA83" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),42),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),42),"")</f>
         <v/>
       </c>
       <c r="AB83" s="1">
@@ -8910,12 +8909,12 @@
       </c>
       <c r="AC83" s="1">
         <f>IF($AA83="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA83,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="84" spans="27:29">
       <c r="AA84" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),43),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),43),"")</f>
         <v/>
       </c>
       <c r="AB84" s="1">
@@ -8924,12 +8923,12 @@
       </c>
       <c r="AC84" s="1">
         <f>IF($AA84="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA84,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="85" spans="27:29">
       <c r="AA85" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),44),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),44),"")</f>
         <v/>
       </c>
       <c r="AB85" s="1">
@@ -8938,12 +8937,12 @@
       </c>
       <c r="AC85" s="1">
         <f>IF($AA85="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA85,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="86" spans="27:29">
       <c r="AA86" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),45),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),45),"")</f>
         <v/>
       </c>
       <c r="AB86" s="1">
@@ -8952,12 +8951,12 @@
       </c>
       <c r="AC86" s="1">
         <f>IF($AA86="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA86,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="87" spans="27:29">
       <c r="AA87" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),46),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),46),"")</f>
         <v/>
       </c>
       <c r="AB87" s="1">
@@ -8966,12 +8965,12 @@
       </c>
       <c r="AC87" s="1">
         <f>IF($AA87="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA87,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="88" spans="27:29">
       <c r="AA88" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),47),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),47),"")</f>
         <v/>
       </c>
       <c r="AB88" s="1">
@@ -8980,12 +8979,12 @@
       </c>
       <c r="AC88" s="1">
         <f>IF($AA88="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA88,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="89" spans="27:29">
       <c r="AA89" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),48),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),48),"")</f>
         <v/>
       </c>
       <c r="AB89" s="1">
@@ -8994,12 +8993,12 @@
       </c>
       <c r="AC89" s="1">
         <f>IF($AA89="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA89,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="90" spans="27:29">
       <c r="AA90" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),49),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),49),"")</f>
         <v/>
       </c>
       <c r="AB90" s="1">
@@ -9008,12 +9007,12 @@
       </c>
       <c r="AC90" s="1">
         <f>IF($AA90="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA90,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="91" spans="27:29">
       <c r="AA91" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),50),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),50),"")</f>
         <v/>
       </c>
       <c r="AB91" s="1">
@@ -9022,12 +9021,12 @@
       </c>
       <c r="AC91" s="1">
         <f>IF($AA91="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA91,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="92" spans="27:29">
       <c r="AA92" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),51),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),51),"")</f>
         <v/>
       </c>
       <c r="AB92" s="1">
@@ -9036,12 +9035,12 @@
       </c>
       <c r="AC92" s="1">
         <f>IF($AA92="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA92,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="93" spans="27:29">
       <c r="AA93" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),52),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),52),"")</f>
         <v/>
       </c>
       <c r="AB93" s="1">
@@ -9050,12 +9049,12 @@
       </c>
       <c r="AC93" s="1">
         <f>IF($AA93="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA93,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="94" spans="27:29">
       <c r="AA94" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),53),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),53),"")</f>
         <v/>
       </c>
       <c r="AB94" s="1">
@@ -9064,12 +9063,12 @@
       </c>
       <c r="AC94" s="1">
         <f>IF($AA94="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA94,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="95" spans="27:29">
       <c r="AA95" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),54),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),54),"")</f>
         <v/>
       </c>
       <c r="AB95" s="1">
@@ -9078,12 +9077,12 @@
       </c>
       <c r="AC95" s="1">
         <f>IF($AA95="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA95,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="96" spans="27:29">
       <c r="AA96" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),55),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),55),"")</f>
         <v/>
       </c>
       <c r="AB96" s="1">
@@ -9092,12 +9091,12 @@
       </c>
       <c r="AC96" s="1">
         <f>IF($AA96="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA96,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="97" spans="27:29">
       <c r="AA97" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),56),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),56),"")</f>
         <v/>
       </c>
       <c r="AB97" s="1">
@@ -9106,12 +9105,12 @@
       </c>
       <c r="AC97" s="1">
         <f>IF($AA97="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA97,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="98" spans="27:29">
       <c r="AA98" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),57),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),57),"")</f>
         <v/>
       </c>
       <c r="AB98" s="1">
@@ -9120,12 +9119,12 @@
       </c>
       <c r="AC98" s="1">
         <f>IF($AA98="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA98,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="99" spans="27:29">
       <c r="AA99" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),58),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),58),"")</f>
         <v/>
       </c>
       <c r="AB99" s="1">
@@ -9134,12 +9133,12 @@
       </c>
       <c r="AC99" s="1">
         <f>IF($AA99="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA99,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="100" spans="27:29">
       <c r="AA100" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),59),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),59),"")</f>
         <v/>
       </c>
       <c r="AB100" s="1">
@@ -9148,12 +9147,12 @@
       </c>
       <c r="AC100" s="1">
         <f>IF($AA100="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA100,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="101" spans="27:29">
       <c r="AA101" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),60),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),60),"")</f>
         <v/>
       </c>
       <c r="AB101" s="1">
@@ -9162,11 +9161,10 @@
       </c>
       <c r="AC101" s="1">
         <f>IF($AA101="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA101,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter>
@@ -10246,7 +10244,6 @@
       <c r="G79" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -10449,7 +10446,7 @@
       </c>
       <c r="G5" s="53"/>
       <c r="H5" s="83" t="str">
-        <f>"Overdue: "&amp;'_Data'!$AF$15&amp;" invoices"</f>
+        <f>"Overdue: "&amp;'_Data'!$AF$15&amp;IF('_Data'!$AF$15=1," invoice"," invoices")</f>
         <v>Overdue: 0 invoices</v>
       </c>
       <c r="I5" s="83"/>
@@ -12193,7 +12190,6 @@
       <c r="C98" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
@@ -13433,7 +13429,6 @@
       <c r="I68" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="28">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -14641,7 +14636,6 @@
       <c r="I53" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
@@ -15475,7 +15469,6 @@
       <c r="C48" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="26">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
@@ -16502,7 +16495,6 @@
     <row r="47" spans="1:14" ht="18" customHeight="1"/>
     <row r="48" spans="1:14" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="28">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
@@ -17849,7 +17841,6 @@
       <c r="J86" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="51">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B3:M3"/>
@@ -17992,7 +17983,7 @@
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="73" t="str">
-        <f>"Tax rate: "&amp;TEXT(TaxRate,"0.0%%")</f>
+        <f>"Tax rate: "&amp;TEXT(TaxRate,"0.0%")</f>
         <v>Tax rate: 0.0%</v>
       </c>
       <c r="E5" s="73"/>
@@ -18136,7 +18127,7 @@
     <row r="20" spans="1:8" ht="19" customHeight="1">
       <c r="A20" s="58"/>
       <c r="B20" s="58">
-        <f>IF($C20="","",ROW()-7)</f>
+        <f>IF($C20="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C20" s="14"/>
@@ -18148,7 +18139,7 @@
     <row r="21" spans="1:8" ht="19" customHeight="1">
       <c r="A21" s="65"/>
       <c r="B21" s="65">
-        <f>IF($C21="","",ROW()-7)</f>
+        <f>IF($C21="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C21" s="9"/>
@@ -18160,7 +18151,7 @@
     <row r="22" spans="1:8" ht="19" customHeight="1">
       <c r="A22" s="58"/>
       <c r="B22" s="58">
-        <f>IF($C22="","",ROW()-7)</f>
+        <f>IF($C22="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C22" s="14"/>
@@ -18172,7 +18163,7 @@
     <row r="23" spans="1:8" ht="19" customHeight="1">
       <c r="A23" s="65"/>
       <c r="B23" s="65">
-        <f>IF($C23="","",ROW()-7)</f>
+        <f>IF($C23="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C23" s="9"/>
@@ -18184,7 +18175,7 @@
     <row r="24" spans="1:8" ht="19" customHeight="1">
       <c r="A24" s="58"/>
       <c r="B24" s="58">
-        <f>IF($C24="","",ROW()-7)</f>
+        <f>IF($C24="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C24" s="14"/>
@@ -18196,7 +18187,7 @@
     <row r="25" spans="1:8" ht="19" customHeight="1">
       <c r="A25" s="65"/>
       <c r="B25" s="65">
-        <f>IF($C25="","",ROW()-7)</f>
+        <f>IF($C25="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C25" s="9"/>
@@ -18208,7 +18199,7 @@
     <row r="26" spans="1:8" ht="19" customHeight="1">
       <c r="A26" s="58"/>
       <c r="B26" s="58">
-        <f>IF($C26="","",ROW()-7)</f>
+        <f>IF($C26="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C26" s="14"/>
@@ -18220,7 +18211,7 @@
     <row r="27" spans="1:8" ht="19" customHeight="1">
       <c r="A27" s="65"/>
       <c r="B27" s="65">
-        <f>IF($C27="","",ROW()-7)</f>
+        <f>IF($C27="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C27" s="9"/>
@@ -18232,7 +18223,7 @@
     <row r="28" spans="1:8" ht="19" customHeight="1">
       <c r="A28" s="58"/>
       <c r="B28" s="58">
-        <f>IF($C28="","",ROW()-7)</f>
+        <f>IF($C28="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C28" s="14"/>
@@ -18244,7 +18235,7 @@
     <row r="29" spans="1:8" ht="19" customHeight="1">
       <c r="A29" s="65"/>
       <c r="B29" s="65">
-        <f>IF($C29="","",ROW()-7)</f>
+        <f>IF($C29="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C29" s="9"/>
@@ -18256,7 +18247,7 @@
     <row r="30" spans="1:8" ht="19" customHeight="1">
       <c r="A30" s="58"/>
       <c r="B30" s="58">
-        <f>IF($C30="","",ROW()-7)</f>
+        <f>IF($C30="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C30" s="14"/>
@@ -18268,7 +18259,7 @@
     <row r="31" spans="1:8" ht="19" customHeight="1">
       <c r="A31" s="65"/>
       <c r="B31" s="65">
-        <f>IF($C31="","",ROW()-7)</f>
+        <f>IF($C31="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C31" s="9"/>
@@ -18280,7 +18271,7 @@
     <row r="32" spans="1:8" ht="19" customHeight="1">
       <c r="A32" s="58"/>
       <c r="B32" s="58">
-        <f>IF($C32="","",ROW()-7)</f>
+        <f>IF($C32="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C32" s="14"/>
@@ -18292,7 +18283,7 @@
     <row r="33" spans="1:8" ht="19" customHeight="1">
       <c r="A33" s="65"/>
       <c r="B33" s="65">
-        <f>IF($C33="","",ROW()-7)</f>
+        <f>IF($C33="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C33" s="9"/>
@@ -18304,7 +18295,7 @@
     <row r="34" spans="1:8" ht="19" customHeight="1">
       <c r="A34" s="58"/>
       <c r="B34" s="58">
-        <f>IF($C34="","",ROW()-7)</f>
+        <f>IF($C34="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C34" s="14"/>
@@ -18316,7 +18307,7 @@
     <row r="35" spans="1:8" ht="19" customHeight="1">
       <c r="A35" s="65"/>
       <c r="B35" s="65">
-        <f>IF($C35="","",ROW()-7)</f>
+        <f>IF($C35="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C35" s="9"/>
@@ -18328,7 +18319,7 @@
     <row r="36" spans="1:8" ht="19" customHeight="1">
       <c r="A36" s="58"/>
       <c r="B36" s="58">
-        <f>IF($C36="","",ROW()-7)</f>
+        <f>IF($C36="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C36" s="14"/>
@@ -18340,7 +18331,7 @@
     <row r="37" spans="1:8" ht="19" customHeight="1">
       <c r="A37" s="65"/>
       <c r="B37" s="65">
-        <f>IF($C37="","",ROW()-7)</f>
+        <f>IF($C37="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C37" s="9"/>
@@ -18352,7 +18343,7 @@
     <row r="38" spans="1:8" ht="19" customHeight="1">
       <c r="A38" s="58"/>
       <c r="B38" s="58">
-        <f>IF($C38="","",ROW()-7)</f>
+        <f>IF($C38="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C38" s="14"/>
@@ -18364,7 +18355,7 @@
     <row r="39" spans="1:8" ht="19" customHeight="1">
       <c r="A39" s="65"/>
       <c r="B39" s="65">
-        <f>IF($C39="","",ROW()-7)</f>
+        <f>IF($C39="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C39" s="9"/>
@@ -18468,7 +18459,6 @@
     <row r="51" ht="19" customHeight="1"/>
     <row r="52" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="16">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -19356,7 +19346,6 @@
     <row r="67" ht="19" customHeight="1"/>
     <row r="68" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="75">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -19517,7 +19506,7 @@
         <v>224</v>
       </c>
       <c r="F4" s="66">
-        <v>46278</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19" customHeight="1">
@@ -19688,7 +19677,7 @@
     </row>
     <row r="24" spans="2:8" ht="19" customHeight="1">
       <c r="D24" s="106" t="str">
-        <f>"Tax ("&amp;TEXT(TaxRate,"0.0%%")&amp;" - from Setup)"</f>
+        <f>"Tax ("&amp;TEXT(TaxRate,"0.0%")&amp;" - from Setup)"</f>
         <v>Tax (0.0% - from Setup)</v>
       </c>
       <c r="E24" s="106"/>
@@ -19709,8 +19698,8 @@
     </row>
     <row r="26" spans="2:8" ht="19" customHeight="1">
       <c r="D26" s="106" t="str">
-        <f>"Deposit to confirm ("&amp;TEXT(DepositPct,"0%%")&amp;" - from Setup)"</f>
-        <v>Deposit to confirm (0% - from Setup)</v>
+        <f>"Deposit to confirm ("&amp;TEXT(DepositPct,"0%")&amp;" - from Setup)"</f>
+        <v>Deposit to confirm (40% - from Setup)</v>
       </c>
       <c r="E26" s="106"/>
       <c r="F26" s="107">
@@ -19874,7 +19863,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="24">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:H2"/>
@@ -20585,7 +20573,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="20">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:H2"/>
@@ -21334,7 +21321,6 @@
     <row r="95" ht="19" customHeight="1"/>
     <row r="96" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="79">
     <mergeCell ref="B5:H7"/>
     <mergeCell ref="B8:H9"/>
@@ -21604,7 +21590,7 @@
     </row>
     <row r="9" spans="2:16" ht="30" customHeight="1">
       <c r="B9" s="40">
-        <f>COUNTIF('📅 Events'!$Q$8:$Q$47,"&lt;&gt;❌ Cancelled")+COUNTIF('📅 Events'!$Q$8:$Q$47,"❌ Cancelled")</f>
+        <f>SUMPRODUCT(('📅 Events'!$Q$8:$Q$47&lt;&gt;"")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled"))</f>
         <v>0</v>
       </c>
       <c r="C9" s="40"/>
@@ -22003,7 +21989,6 @@
     <row r="89" ht="18" customHeight="1"/>
     <row r="90" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="65">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="K2:P2"/>
@@ -23260,7 +23245,6 @@
       <c r="K57" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
@@ -23435,7 +23419,7 @@
     <row r="4" spans="2:18" ht="7" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:18" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="50" t="str">
-        <f>"Bookings: "&amp;COUNTIF('📅 Events'!$Q$8:$Q$47,"&lt;&gt;❌ Cancelled")</f>
+        <f>"Bookings: "&amp;SUMPRODUCT(('📅 Events'!$Q$8:$Q$47&lt;&gt;"")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled"))</f>
         <v>Bookings: 0</v>
       </c>
       <c r="C5" s="50"/>
@@ -24758,30 +24742,30 @@
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
       <c r="G48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$G$8:$G$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$G$8:$G$47)</f>
         <v>0</v>
       </c>
       <c r="H48" s="71"/>
       <c r="I48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$I$8:$I$47)</f>
         <v>0</v>
       </c>
       <c r="J48" s="71"/>
       <c r="K48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$K$8:$K$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$K$8:$K$47)</f>
         <v>0</v>
       </c>
       <c r="L48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$L$8:$L$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$L$8:$L$47)</f>
         <v>0</v>
       </c>
       <c r="M48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$M$8:$M$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$M$8:$M$47)</f>
         <v>0</v>
       </c>
       <c r="N48" s="71"/>
       <c r="O48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$O$8:$O$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$O$8:$O$47)</f>
         <v>0</v>
       </c>
       <c r="P48" s="72">
@@ -24914,7 +24898,6 @@
       <c r="G57" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B3:O3"/>
@@ -25268,7 +25251,7 @@
     <row r="23" spans="1:7" ht="21" customHeight="1"/>
     <row r="24" spans="1:7" ht="21" customHeight="1">
       <c r="B24" s="82">
-        <f>IF($E$16="","",Currency&amp;TEXT($E$16,"#,##0.00")&amp;"  for the event   ·   "&amp;Currency&amp;TEXT($E$17,"#,##0.00")&amp;" per guest")</f>
+        <f>IF($E$16="","",Currency&amp;TEXT($E$16,"#,##0.00")&amp;" for the event   ·   "&amp;Currency&amp;TEXT($E$17,"#,##0.00")&amp;" per guest")</f>
         <v/>
       </c>
       <c r="C24" s="82"/>
@@ -25426,7 +25409,6 @@
       <c r="C41" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -26398,7 +26380,6 @@
       <c r="I68" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -27673,7 +27654,6 @@
       <c r="I58" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
@@ -27913,7 +27893,7 @@
       <c r="D8" s="14"/>
       <c r="E8" s="85"/>
       <c r="F8" s="88">
-        <f>IF($D8="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D8,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D8="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D8,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G8" s="88">
@@ -27922,7 +27902,7 @@
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="63">
-        <f>IF(OR($G8="",NOT(ISNUMBER($G8))),"",ROUND($G8*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D8,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G8="",NOT(ISNUMBER($G8))),"",ROUND($G8*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D8,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J8" s="89"/>
@@ -27938,7 +27918,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="87"/>
       <c r="F9" s="88">
-        <f>IF($D9="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D9,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D9="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D9,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G9" s="88">
@@ -27947,7 +27927,7 @@
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="63">
-        <f>IF(OR($G9="",NOT(ISNUMBER($G9))),"",ROUND($G9*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D9,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G9="",NOT(ISNUMBER($G9))),"",ROUND($G9*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D9,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J9" s="90"/>
@@ -27963,7 +27943,7 @@
       <c r="D10" s="14"/>
       <c r="E10" s="85"/>
       <c r="F10" s="88">
-        <f>IF($D10="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D10,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D10="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D10,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G10" s="88">
@@ -27972,7 +27952,7 @@
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="63">
-        <f>IF(OR($G10="",NOT(ISNUMBER($G10))),"",ROUND($G10*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D10,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G10="",NOT(ISNUMBER($G10))),"",ROUND($G10*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D10,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J10" s="89"/>
@@ -27988,7 +27968,7 @@
       <c r="D11" s="9"/>
       <c r="E11" s="87"/>
       <c r="F11" s="88">
-        <f>IF($D11="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D11,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D11="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D11,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G11" s="88">
@@ -27997,7 +27977,7 @@
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="63">
-        <f>IF(OR($G11="",NOT(ISNUMBER($G11))),"",ROUND($G11*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D11,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G11="",NOT(ISNUMBER($G11))),"",ROUND($G11*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D11,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J11" s="90"/>
@@ -28013,7 +27993,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="85"/>
       <c r="F12" s="88">
-        <f>IF($D12="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D12,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D12="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D12,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G12" s="88">
@@ -28022,7 +28002,7 @@
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="63">
-        <f>IF(OR($G12="",NOT(ISNUMBER($G12))),"",ROUND($G12*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D12,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G12="",NOT(ISNUMBER($G12))),"",ROUND($G12*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D12,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J12" s="89"/>
@@ -28038,7 +28018,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="87"/>
       <c r="F13" s="88">
-        <f>IF($D13="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D13,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D13="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D13,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G13" s="88">
@@ -28047,7 +28027,7 @@
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="63">
-        <f>IF(OR($G13="",NOT(ISNUMBER($G13))),"",ROUND($G13*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D13,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G13="",NOT(ISNUMBER($G13))),"",ROUND($G13*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D13,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J13" s="90"/>
@@ -28063,7 +28043,7 @@
       <c r="D14" s="14"/>
       <c r="E14" s="85"/>
       <c r="F14" s="88">
-        <f>IF($D14="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D14,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D14="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D14,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G14" s="88">
@@ -28072,7 +28052,7 @@
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="63">
-        <f>IF(OR($G14="",NOT(ISNUMBER($G14))),"",ROUND($G14*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D14,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G14="",NOT(ISNUMBER($G14))),"",ROUND($G14*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D14,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J14" s="89"/>
@@ -28088,7 +28068,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="87"/>
       <c r="F15" s="88">
-        <f>IF($D15="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D15,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D15="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D15,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G15" s="88">
@@ -28097,7 +28077,7 @@
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="63">
-        <f>IF(OR($G15="",NOT(ISNUMBER($G15))),"",ROUND($G15*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D15,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G15="",NOT(ISNUMBER($G15))),"",ROUND($G15*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D15,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J15" s="90"/>
@@ -28113,7 +28093,7 @@
       <c r="D16" s="14"/>
       <c r="E16" s="85"/>
       <c r="F16" s="88">
-        <f>IF($D16="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D16,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D16="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D16,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G16" s="88">
@@ -28122,7 +28102,7 @@
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="63">
-        <f>IF(OR($G16="",NOT(ISNUMBER($G16))),"",ROUND($G16*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D16,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G16="",NOT(ISNUMBER($G16))),"",ROUND($G16*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D16,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J16" s="89"/>
@@ -28138,7 +28118,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="87"/>
       <c r="F17" s="88">
-        <f>IF($D17="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D17,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D17="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D17,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G17" s="88">
@@ -28147,7 +28127,7 @@
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="63">
-        <f>IF(OR($G17="",NOT(ISNUMBER($G17))),"",ROUND($G17*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D17,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G17="",NOT(ISNUMBER($G17))),"",ROUND($G17*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D17,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J17" s="90"/>
@@ -28163,7 +28143,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="85"/>
       <c r="F18" s="88">
-        <f>IF($D18="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D18,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D18="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D18,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G18" s="88">
@@ -28172,7 +28152,7 @@
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="63">
-        <f>IF(OR($G18="",NOT(ISNUMBER($G18))),"",ROUND($G18*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D18,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G18="",NOT(ISNUMBER($G18))),"",ROUND($G18*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D18,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J18" s="89"/>
@@ -28188,7 +28168,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="87"/>
       <c r="F19" s="88">
-        <f>IF($D19="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D19,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D19="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D19,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G19" s="88">
@@ -28197,7 +28177,7 @@
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="63">
-        <f>IF(OR($G19="",NOT(ISNUMBER($G19))),"",ROUND($G19*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D19,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G19="",NOT(ISNUMBER($G19))),"",ROUND($G19*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D19,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J19" s="90"/>
@@ -28213,7 +28193,7 @@
       <c r="D20" s="14"/>
       <c r="E20" s="85"/>
       <c r="F20" s="88">
-        <f>IF($D20="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D20,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D20="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D20,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G20" s="88">
@@ -28222,7 +28202,7 @@
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="63">
-        <f>IF(OR($G20="",NOT(ISNUMBER($G20))),"",ROUND($G20*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D20,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G20="",NOT(ISNUMBER($G20))),"",ROUND($G20*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D20,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J20" s="89"/>
@@ -28238,7 +28218,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="87"/>
       <c r="F21" s="88">
-        <f>IF($D21="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D21,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D21="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D21,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G21" s="88">
@@ -28247,7 +28227,7 @@
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="63">
-        <f>IF(OR($G21="",NOT(ISNUMBER($G21))),"",ROUND($G21*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D21,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G21="",NOT(ISNUMBER($G21))),"",ROUND($G21*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D21,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J21" s="90"/>
@@ -28263,7 +28243,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="85"/>
       <c r="F22" s="88">
-        <f>IF($D22="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D22,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D22="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D22,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G22" s="88">
@@ -28272,7 +28252,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="63">
-        <f>IF(OR($G22="",NOT(ISNUMBER($G22))),"",ROUND($G22*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D22,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G22="",NOT(ISNUMBER($G22))),"",ROUND($G22*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D22,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J22" s="89"/>
@@ -28288,7 +28268,7 @@
       <c r="D23" s="9"/>
       <c r="E23" s="87"/>
       <c r="F23" s="88">
-        <f>IF($D23="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D23,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D23="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D23,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G23" s="88">
@@ -28297,7 +28277,7 @@
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="63">
-        <f>IF(OR($G23="",NOT(ISNUMBER($G23))),"",ROUND($G23*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D23,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G23="",NOT(ISNUMBER($G23))),"",ROUND($G23*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D23,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J23" s="90"/>
@@ -28313,7 +28293,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="85"/>
       <c r="F24" s="88">
-        <f>IF($D24="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D24,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D24="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D24,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G24" s="88">
@@ -28322,7 +28302,7 @@
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="63">
-        <f>IF(OR($G24="",NOT(ISNUMBER($G24))),"",ROUND($G24*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D24,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G24="",NOT(ISNUMBER($G24))),"",ROUND($G24*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D24,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J24" s="89"/>
@@ -28338,7 +28318,7 @@
       <c r="D25" s="9"/>
       <c r="E25" s="87"/>
       <c r="F25" s="88">
-        <f>IF($D25="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D25,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D25="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D25,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G25" s="88">
@@ -28347,7 +28327,7 @@
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="63">
-        <f>IF(OR($G25="",NOT(ISNUMBER($G25))),"",ROUND($G25*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D25,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G25="",NOT(ISNUMBER($G25))),"",ROUND($G25*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D25,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J25" s="90"/>
@@ -28363,7 +28343,7 @@
       <c r="D26" s="14"/>
       <c r="E26" s="85"/>
       <c r="F26" s="88">
-        <f>IF($D26="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D26,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D26="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D26,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G26" s="88">
@@ -28372,7 +28352,7 @@
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="63">
-        <f>IF(OR($G26="",NOT(ISNUMBER($G26))),"",ROUND($G26*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D26,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G26="",NOT(ISNUMBER($G26))),"",ROUND($G26*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D26,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J26" s="89"/>
@@ -28388,7 +28368,7 @@
       <c r="D27" s="9"/>
       <c r="E27" s="87"/>
       <c r="F27" s="88">
-        <f>IF($D27="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D27,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D27="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D27,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G27" s="88">
@@ -28397,7 +28377,7 @@
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="63">
-        <f>IF(OR($G27="",NOT(ISNUMBER($G27))),"",ROUND($G27*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D27,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G27="",NOT(ISNUMBER($G27))),"",ROUND($G27*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D27,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J27" s="90"/>
@@ -28413,7 +28393,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="85"/>
       <c r="F28" s="88">
-        <f>IF($D28="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D28,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D28="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D28,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G28" s="88">
@@ -28422,7 +28402,7 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="63">
-        <f>IF(OR($G28="",NOT(ISNUMBER($G28))),"",ROUND($G28*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D28,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G28="",NOT(ISNUMBER($G28))),"",ROUND($G28*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D28,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J28" s="89"/>
@@ -28438,7 +28418,7 @@
       <c r="D29" s="9"/>
       <c r="E29" s="87"/>
       <c r="F29" s="88">
-        <f>IF($D29="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D29,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D29="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D29,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G29" s="88">
@@ -28447,7 +28427,7 @@
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="63">
-        <f>IF(OR($G29="",NOT(ISNUMBER($G29))),"",ROUND($G29*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D29,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G29="",NOT(ISNUMBER($G29))),"",ROUND($G29*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D29,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J29" s="90"/>
@@ -28463,7 +28443,7 @@
       <c r="D30" s="14"/>
       <c r="E30" s="85"/>
       <c r="F30" s="88">
-        <f>IF($D30="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D30,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D30="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D30,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G30" s="88">
@@ -28472,7 +28452,7 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="63">
-        <f>IF(OR($G30="",NOT(ISNUMBER($G30))),"",ROUND($G30*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D30,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G30="",NOT(ISNUMBER($G30))),"",ROUND($G30*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D30,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J30" s="89"/>
@@ -28488,7 +28468,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="87"/>
       <c r="F31" s="88">
-        <f>IF($D31="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D31,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D31="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D31,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G31" s="88">
@@ -28497,7 +28477,7 @@
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="63">
-        <f>IF(OR($G31="",NOT(ISNUMBER($G31))),"",ROUND($G31*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D31,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G31="",NOT(ISNUMBER($G31))),"",ROUND($G31*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D31,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J31" s="90"/>
@@ -28513,7 +28493,7 @@
       <c r="D32" s="14"/>
       <c r="E32" s="85"/>
       <c r="F32" s="88">
-        <f>IF($D32="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D32,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D32="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D32,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G32" s="88">
@@ -28522,7 +28502,7 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="63">
-        <f>IF(OR($G32="",NOT(ISNUMBER($G32))),"",ROUND($G32*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D32,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G32="",NOT(ISNUMBER($G32))),"",ROUND($G32*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D32,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J32" s="89"/>
@@ -28538,7 +28518,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="87"/>
       <c r="F33" s="88">
-        <f>IF($D33="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D33,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D33="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D33,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G33" s="88">
@@ -28547,7 +28527,7 @@
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="63">
-        <f>IF(OR($G33="",NOT(ISNUMBER($G33))),"",ROUND($G33*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D33,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G33="",NOT(ISNUMBER($G33))),"",ROUND($G33*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D33,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J33" s="90"/>
@@ -28563,7 +28543,7 @@
       <c r="D34" s="14"/>
       <c r="E34" s="85"/>
       <c r="F34" s="88">
-        <f>IF($D34="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D34,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D34="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D34,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G34" s="88">
@@ -28572,7 +28552,7 @@
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="63">
-        <f>IF(OR($G34="",NOT(ISNUMBER($G34))),"",ROUND($G34*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D34,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G34="",NOT(ISNUMBER($G34))),"",ROUND($G34*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D34,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J34" s="89"/>
@@ -28588,7 +28568,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="87"/>
       <c r="F35" s="88">
-        <f>IF($D35="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D35,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D35="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D35,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G35" s="88">
@@ -28597,7 +28577,7 @@
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="63">
-        <f>IF(OR($G35="",NOT(ISNUMBER($G35))),"",ROUND($G35*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D35,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G35="",NOT(ISNUMBER($G35))),"",ROUND($G35*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D35,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J35" s="90"/>
@@ -28613,7 +28593,7 @@
       <c r="D36" s="14"/>
       <c r="E36" s="85"/>
       <c r="F36" s="88">
-        <f>IF($D36="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D36,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D36="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D36,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G36" s="88">
@@ -28622,7 +28602,7 @@
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="63">
-        <f>IF(OR($G36="",NOT(ISNUMBER($G36))),"",ROUND($G36*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D36,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G36="",NOT(ISNUMBER($G36))),"",ROUND($G36*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D36,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J36" s="89"/>
@@ -28638,7 +28618,7 @@
       <c r="D37" s="9"/>
       <c r="E37" s="87"/>
       <c r="F37" s="88">
-        <f>IF($D37="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D37,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D37="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D37,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G37" s="88">
@@ -28647,7 +28627,7 @@
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="63">
-        <f>IF(OR($G37="",NOT(ISNUMBER($G37))),"",ROUND($G37*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D37,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G37="",NOT(ISNUMBER($G37))),"",ROUND($G37*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D37,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J37" s="90"/>
@@ -28663,7 +28643,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="85"/>
       <c r="F38" s="88">
-        <f>IF($D38="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D38,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D38="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D38,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G38" s="88">
@@ -28672,7 +28652,7 @@
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="63">
-        <f>IF(OR($G38="",NOT(ISNUMBER($G38))),"",ROUND($G38*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D38,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G38="",NOT(ISNUMBER($G38))),"",ROUND($G38*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D38,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J38" s="89"/>
@@ -28688,7 +28668,7 @@
       <c r="D39" s="9"/>
       <c r="E39" s="87"/>
       <c r="F39" s="88">
-        <f>IF($D39="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D39,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D39="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D39,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G39" s="88">
@@ -28697,7 +28677,7 @@
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="63">
-        <f>IF(OR($G39="",NOT(ISNUMBER($G39))),"",ROUND($G39*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D39,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G39="",NOT(ISNUMBER($G39))),"",ROUND($G39*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D39,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J39" s="90"/>
@@ -28713,7 +28693,7 @@
       <c r="D40" s="14"/>
       <c r="E40" s="85"/>
       <c r="F40" s="88">
-        <f>IF($D40="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D40,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D40="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D40,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G40" s="88">
@@ -28722,7 +28702,7 @@
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="63">
-        <f>IF(OR($G40="",NOT(ISNUMBER($G40))),"",ROUND($G40*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D40,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G40="",NOT(ISNUMBER($G40))),"",ROUND($G40*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D40,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J40" s="89"/>
@@ -28738,7 +28718,7 @@
       <c r="D41" s="9"/>
       <c r="E41" s="87"/>
       <c r="F41" s="88">
-        <f>IF($D41="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D41,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D41="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D41,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G41" s="88">
@@ -28747,7 +28727,7 @@
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="63">
-        <f>IF(OR($G41="",NOT(ISNUMBER($G41))),"",ROUND($G41*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D41,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G41="",NOT(ISNUMBER($G41))),"",ROUND($G41*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D41,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J41" s="90"/>
@@ -28763,7 +28743,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="85"/>
       <c r="F42" s="88">
-        <f>IF($D42="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D42,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D42="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D42,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G42" s="88">
@@ -28772,7 +28752,7 @@
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="63">
-        <f>IF(OR($G42="",NOT(ISNUMBER($G42))),"",ROUND($G42*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D42,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G42="",NOT(ISNUMBER($G42))),"",ROUND($G42*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D42,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J42" s="89"/>
@@ -28788,7 +28768,7 @@
       <c r="D43" s="9"/>
       <c r="E43" s="87"/>
       <c r="F43" s="88">
-        <f>IF($D43="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D43,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D43="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D43,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G43" s="88">
@@ -28797,7 +28777,7 @@
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="63">
-        <f>IF(OR($G43="",NOT(ISNUMBER($G43))),"",ROUND($G43*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D43,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G43="",NOT(ISNUMBER($G43))),"",ROUND($G43*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D43,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J43" s="90"/>
@@ -28813,7 +28793,7 @@
       <c r="D44" s="14"/>
       <c r="E44" s="85"/>
       <c r="F44" s="88">
-        <f>IF($D44="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D44,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D44="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D44,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G44" s="88">
@@ -28822,7 +28802,7 @@
       </c>
       <c r="H44" s="14"/>
       <c r="I44" s="63">
-        <f>IF(OR($G44="",NOT(ISNUMBER($G44))),"",ROUND($G44*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D44,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G44="",NOT(ISNUMBER($G44))),"",ROUND($G44*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D44,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J44" s="89"/>
@@ -28838,7 +28818,7 @@
       <c r="D45" s="9"/>
       <c r="E45" s="87"/>
       <c r="F45" s="88">
-        <f>IF($D45="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D45,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D45="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D45,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G45" s="88">
@@ -28847,7 +28827,7 @@
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="63">
-        <f>IF(OR($G45="",NOT(ISNUMBER($G45))),"",ROUND($G45*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D45,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G45="",NOT(ISNUMBER($G45))),"",ROUND($G45*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D45,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J45" s="90"/>
@@ -28863,7 +28843,7 @@
       <c r="D46" s="14"/>
       <c r="E46" s="85"/>
       <c r="F46" s="88">
-        <f>IF($D46="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D46,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D46="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D46,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G46" s="88">
@@ -28872,7 +28852,7 @@
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="63">
-        <f>IF(OR($G46="",NOT(ISNUMBER($G46))),"",ROUND($G46*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D46,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G46="",NOT(ISNUMBER($G46))),"",ROUND($G46*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D46,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J46" s="89"/>
@@ -28888,7 +28868,7 @@
       <c r="D47" s="9"/>
       <c r="E47" s="87"/>
       <c r="F47" s="88">
-        <f>IF($D47="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D47,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D47="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D47,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G47" s="88">
@@ -28897,7 +28877,7 @@
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="63">
-        <f>IF(OR($G47="",NOT(ISNUMBER($G47))),"",ROUND($G47*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D47,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G47="",NOT(ISNUMBER($G47))),"",ROUND($G47*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D47,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J47" s="90"/>
@@ -28915,7 +28895,7 @@
       <c r="G48" s="70"/>
       <c r="H48" s="71"/>
       <c r="I48" s="84">
-        <f>SUMPRODUCT(('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓")*('🛒 Shopping List'!$D$8:$D$47&lt;&gt;"")*'🛒 Shopping List'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(--(('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓")*('🛒 Shopping List'!$D$8:$D$47&lt;&gt;"")),'🛒 Shopping List'!$I$8:$I$47)</f>
         <v>0</v>
       </c>
       <c r="J48" s="71"/>
@@ -29035,7 +29015,6 @@
       <c r="I58" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="28">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>

--- a/products/Catering_Business_Manager_PREMIUM_Classic.xlsx
+++ b/products/Catering_Business_Manager_PREMIUM_Classic.xlsx
@@ -19425,7 +19425,7 @@
   </mergeCells>
   <conditionalFormatting sqref="B10:B58">
     <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
-      <formula>✓</formula>
+      <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -20597,7 +20597,7 @@
   </mergeCells>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Currency symbol" prompt="Pick a symbol, or type your own (e.g. Rs)." sqref="C9:D9">
-      <formula1>$,€,£,¥,₨,₹,A$,C$,R,kr,CHF</formula1>
+      <formula1>"$,€,£,¥,₨,₹,A$,C$,R,kr,CHF"</formula1>
     </dataValidation>
     <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Pick a percentage" error="Enter a share of the price between 0% and 50%." sqref="C11:D11">
       <formula1>0</formula1>
